--- a/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-UI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3881AE9C-3E90-4132-8A7A-F811FD225368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91F1122-9BB6-4F5B-8BF9-D696A7225D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="672" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1992" yWindow="6192" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
 This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
@@ -60,23 +60,52 @@
     <t>en</t>
   </si>
   <si>
-    <t>本作含有&lt;color=#FF0000&gt;轻微暴力及紧张&lt;/color&gt;场面，建议 12 岁以上玩家游玩</t>
-  </si>
-  <si>
-    <t>本作所有剧情与角色均为&lt;color=#FF0000&gt;虚构&lt;/color&gt;，如有雷同，实属巧合</t>
-  </si>
-  <si>
-    <t>This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
-</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFCC00&gt;Game Tip: Press Space or click to continue the dialogue&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#FFCC00&gt;游戏提示: 按空格或点击鼠标进行对话</t>
+    <t>这个点……应该没人吧？</t>
+  </si>
+  <si>
+    <t>可千万别有人……总算溜上来了</t>
+  </si>
+  <si>
+    <t>&lt;color=#FF0000&gt;逃课上来要是被抓，那可就不是写检讨那么简单了&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>学校纪律处的那帮人，一张处分单下来，这学期直接就完蛋了</t>
+  </si>
+  <si>
+    <t>刚才在五楼楼梯口，差点跟教务主任对脸撞上</t>
+  </si>
+  <si>
+    <t>他正盯着文件往楼下走，我贴在冰凉的墙面上，呼吸都快停了</t>
+  </si>
+  <si>
+    <t>幸好他突然拐进办公室了……吓死我了</t>
+  </si>
+  <si>
+    <t>终于到学校天台了！反正这节课我是不会回去了</t>
+  </si>
+  <si>
+    <t>This time of day... nobody should be around, yeah?</t>
+  </si>
+  <si>
+    <t>Please let no one be here... finally snuck up.</t>
+  </si>
+  <si>
+    <t>&lt;color=#FF0000&gt;If I get busted for ditching up here, it’s way more than writing a reflection.&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>One ticket from Discipline and my semester’s done.</t>
+  </si>
+  <si>
+    <t>Finally made it to the rooftop! I’m not going back to class this period anyway.</t>
+  </si>
+  <si>
+    <t>I nearly ran face-first into the dean at the fifth-floor stairwell just now.</t>
+  </si>
+  <si>
+    <t>Thankfully, he veered into his office... I was terrified.</t>
+  </si>
+  <si>
+    <t>He was fixed on his documents as he descended; I pressed to the frigid wall, breath all but stilled.</t>
   </si>
 </sst>
 </file>
@@ -397,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.21875" customWidth="1"/>
@@ -412,28 +441,68 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-UI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91F1122-9BB6-4F5B-8BF9-D696A7225D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A296708D-5400-4199-B714-654729358C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1992" yWindow="6192" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2196" yWindow="4404" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
 This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
@@ -60,52 +60,70 @@
     <t>en</t>
   </si>
   <si>
-    <t>这个点……应该没人吧？</t>
-  </si>
-  <si>
-    <t>可千万别有人……总算溜上来了</t>
-  </si>
-  <si>
     <t>&lt;color=#FF0000&gt;逃课上来要是被抓，那可就不是写检讨那么简单了&lt;/color&gt;</t>
   </si>
   <si>
     <t>学校纪律处的那帮人，一张处分单下来，这学期直接就完蛋了</t>
   </si>
   <si>
-    <t>刚才在五楼楼梯口，差点跟教务主任对脸撞上</t>
-  </si>
-  <si>
-    <t>他正盯着文件往楼下走，我贴在冰凉的墙面上，呼吸都快停了</t>
-  </si>
-  <si>
     <t>幸好他突然拐进办公室了……吓死我了</t>
   </si>
   <si>
-    <t>终于到学校天台了！反正这节课我是不会回去了</t>
-  </si>
-  <si>
-    <t>This time of day... nobody should be around, yeah?</t>
-  </si>
-  <si>
-    <t>Please let no one be here... finally snuck up.</t>
-  </si>
-  <si>
-    <t>&lt;color=#FF0000&gt;If I get busted for ditching up here, it’s way more than writing a reflection.&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>One ticket from Discipline and my semester’s done.</t>
-  </si>
-  <si>
-    <t>Finally made it to the rooftop! I’m not going back to class this period anyway.</t>
-  </si>
-  <si>
-    <t>I nearly ran face-first into the dean at the fifth-floor stairwell just now.</t>
-  </si>
-  <si>
-    <t>Thankfully, he veered into his office... I was terrified.</t>
-  </si>
-  <si>
-    <t>He was fixed on his documents as he descended; I pressed to the frigid wall, breath all but stilled.</t>
+    <t>哈……哈……这鬼楼梯……总算……上来了……</t>
+  </si>
+  <si>
+    <t>我侧身挤进铁门，整个人几乎虚脱，靠在门板上大口喘气</t>
+  </si>
+  <si>
+    <t>缺乏锻炼的下场就是，爬这六层楼简直要了半条命，我像条脱水的鱼一样大口喘气</t>
+  </si>
+  <si>
+    <t>这个点……学校天台应该没人吧？</t>
+  </si>
+  <si>
+    <t>可千万别有人……好不容易才溜上来</t>
+  </si>
+  <si>
+    <t>刚才在五楼楼梯口，差点就跟下楼的教务主任对脸撞上</t>
+  </si>
+  <si>
+    <t>他正盯着文件往楼下走，我贴在冰凉的侧墙上，呼吸都快停了</t>
+  </si>
+  <si>
+    <t>终于到学校天台了！反正这节课我是绝对不会回去了</t>
+  </si>
+  <si>
+    <t>I squeezed sideways through the iron door, utterly spent, leaning against the door and gulping for air.</t>
+  </si>
+  <si>
+    <t>This is what a lack of exercise gets you—climbing six floors almost cost me half my life. I’m gasping like a fish out of water.</t>
+  </si>
+  <si>
+    <t>At this hour... there shouldn’t be anyone on the school rooftop, right?</t>
+  </si>
+  <si>
+    <t>Please let there be no one... it took so much effort to sneak up here.</t>
+  </si>
+  <si>
+    <t>&lt;color=#FF0000&gt;If I get caught cutting class to come up here, it won’t just be writing a self-criticism.&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Those people in the discipline office—one disciplinary notice and this semester is basically over.</t>
+  </si>
+  <si>
+    <t>Luckily he suddenly turned into an office... scared me to death.</t>
+  </si>
+  <si>
+    <t>Finally made it to the school rooftop! Anyway, I’m definitely not going back to class this period.</t>
+  </si>
+  <si>
+    <t>Back at the fifth-floor landing, I almost smashed face-first into the academic dean coming down.</t>
+  </si>
+  <si>
+    <t>He was staring at his documents as he walked downstairs; I pressed against the cold side wall, barely breathing.</t>
+  </si>
+  <si>
+    <t>Ha... ha... this damned staircase... finally... made it up…</t>
   </si>
 </sst>
 </file>
@@ -426,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.21875" customWidth="1"/>
@@ -443,47 +461,47 @@
     </row>
     <row r="2" spans="1:2" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -491,18 +509,42 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-UI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A296708D-5400-4199-B714-654729358C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1413322-4EC0-44C0-B69E-8E005E3B9B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2196" yWindow="4404" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2760" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -117,13 +117,13 @@
     <t>Finally made it to the school rooftop! Anyway, I’m definitely not going back to class this period.</t>
   </si>
   <si>
-    <t>Back at the fifth-floor landing, I almost smashed face-first into the academic dean coming down.</t>
-  </si>
-  <si>
     <t>He was staring at his documents as he walked downstairs; I pressed against the cold side wall, barely breathing.</t>
   </si>
   <si>
     <t>Ha... ha... this damned staircase... finally... made it up…</t>
+  </si>
+  <si>
+    <t>Back at the fifth-floor landing, I almost smashed face-first into the Academic Affairs Director coming down.</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -528,7 +528,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">

--- a/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/1-Scene-UI/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\1-Scene-UI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1413322-4EC0-44C0-B69E-8E005E3B9B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB366CFC-B6BE-4453-9E59-C6072D2A3B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2760" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8064" yWindow="2808" windowWidth="16272" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -72,12 +72,6 @@
     <t>哈……哈……这鬼楼梯……总算……上来了……</t>
   </si>
   <si>
-    <t>我侧身挤进铁门，整个人几乎虚脱，靠在门板上大口喘气</t>
-  </si>
-  <si>
-    <t>缺乏锻炼的下场就是，爬这六层楼简直要了半条命，我像条脱水的鱼一样大口喘气</t>
-  </si>
-  <si>
     <t>这个点……学校天台应该没人吧？</t>
   </si>
   <si>
@@ -93,12 +87,6 @@
     <t>终于到学校天台了！反正这节课我是绝对不会回去了</t>
   </si>
   <si>
-    <t>I squeezed sideways through the iron door, utterly spent, leaning against the door and gulping for air.</t>
-  </si>
-  <si>
-    <t>This is what a lack of exercise gets you—climbing six floors almost cost me half my life. I’m gasping like a fish out of water.</t>
-  </si>
-  <si>
     <t>At this hour... there shouldn’t be anyone on the school rooftop, right?</t>
   </si>
   <si>
@@ -124,6 +112,18 @@
   </si>
   <si>
     <t>Back at the fifth-floor landing, I almost smashed face-first into the Academic Affairs Director coming down.</t>
+  </si>
+  <si>
+    <t>我侧身挤进铁门，整个人几乎虚脱</t>
+  </si>
+  <si>
+    <t>缺乏锻炼的下场就是，爬到六楼简直要了半条命，我双腿发软，像条脱水的鱼一样大口喘气</t>
+  </si>
+  <si>
+    <t>I turned sideways and squeezed through the iron door, nearly spent.</t>
+  </si>
+  <si>
+    <t>That’s the price of skipping exercise—by the sixth floor I was half dead, my legs jelly, gulping air like a fish out of water.</t>
   </si>
 </sst>
 </file>
@@ -447,7 +447,7 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="67.21875" customWidth="1"/>
+    <col min="1" max="1" width="74.109375" customWidth="1"/>
     <col min="2" max="2" width="67.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -464,39 +464,39 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -504,7 +504,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -512,23 +512,23 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -536,15 +536,15 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
